--- a/Project_ETF/ETF_Investment_Portfolio/00981A/ETF_Investment_Portfolio_20260610.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00981A/ETF_Investment_Portfolio_20260610.xlsx
@@ -997,220 +997,220 @@
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>C_NTD</t>
+          <t>6515</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>CASH</t>
+          <t>穎崴</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>4,563,458,507</t>
+          <t>442,000</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>1.67%</t>
+          <t>1.32%</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>6515</t>
+          <t>8210</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>穎崴</t>
+          <t>勤誠</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>442,000</t>
+          <t>2,267,000</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>1.32%</t>
+          <t>1.20%</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>8210</t>
+          <t>6805</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>勤誠</t>
+          <t>富世達</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>2,267,000</t>
+          <t>1,761,000</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>1.20%</t>
+          <t>1.13%</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>6805</t>
+          <t>6510</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>富世達</t>
+          <t>精測</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>1,761,000</t>
+          <t>930,000</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>1.13%</t>
+          <t>1.09%</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>6510</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>精測</t>
+          <t>鴻海</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>930,000</t>
+          <t>7,307,000</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>1.09%</t>
+          <t>0.71%</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>3533</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>鴻海</t>
+          <t>嘉澤</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>7,307,000</t>
+          <t>852,000</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>0.71%</t>
+          <t>0.68%</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>3533</t>
+          <t>6187</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>嘉澤</t>
+          <t>萬潤</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>852,000</t>
+          <t>1,334,000</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>0.68%</t>
+          <t>0.52%</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>6187</t>
+          <t>2404</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>萬潤</t>
+          <t>漢唐</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>1,334,000</t>
+          <t>1,200,000</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>0.52%</t>
+          <t>0.51%</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>2404</t>
+          <t>6147</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>漢唐</t>
+          <t>頎邦</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>1,200,000</t>
+          <t>5,775,000</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>0.51%</t>
+          <t>0.48%</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>6147</t>
+          <t>5439</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>頎邦</t>
+          <t>高技</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>5,775,000</t>
+          <t>3,528,000</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>0.48%</t>
+          <t>0.46%</t>
         </is>
       </c>
     </row>
@@ -1239,110 +1239,110 @@
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>5439</t>
+          <t>4966</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>高技</t>
+          <t>譜瑞-KY</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>3,528,000</t>
+          <t>1,642,000</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>0.46%</t>
+          <t>0.40%</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>4966</t>
+          <t>8150</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>譜瑞-KY</t>
+          <t>南茂</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>1,642,000</t>
+          <t>11,635,000</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>0.40%</t>
+          <t>0.38%</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>8150</t>
+          <t>2449</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>南茂</t>
+          <t>京元電子</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>11,635,000</t>
+          <t>3,645,000</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>0.38%</t>
+          <t>0.36%</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>2449</t>
+          <t>6278</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>京元電子</t>
+          <t>台表科</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>3,645,000</t>
+          <t>3,734,000</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>0.36%</t>
+          <t>0.26%</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>6278</t>
+          <t>3443</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>台表科</t>
+          <t>創意</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>3,734,000</t>
+          <t>167,000</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>0.26%</t>
+          <t>0.25%</t>
         </is>
       </c>
     </row>
@@ -1371,198 +1371,198 @@
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>3443</t>
+          <t>8358</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>創意</t>
+          <t>金居</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>167,000</t>
+          <t>980,000</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>0.25%</t>
+          <t>0.20%</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>8358</t>
+          <t>3376</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>金居</t>
+          <t>新日興</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>980,000</t>
+          <t>1,741,000</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>0.20%</t>
+          <t>0.14%</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>M_NTD</t>
+          <t>6191</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>MARGIN</t>
+          <t>精成科</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>500,128,241</t>
+          <t>3,988,000</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t>0.18%</t>
+          <t>0.14%</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>3376</t>
+          <t>6271</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>新日興</t>
+          <t>同欣電</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>1,741,000</t>
+          <t>686,000</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>0.14%</t>
+          <t>0.06%</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>6191</t>
+          <t>2002</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>精成科</t>
+          <t>中鋼</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>3,988,000</t>
+          <t>5,163,000</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
         <is>
-          <t>0.14%</t>
+          <t>0.04%</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>6271</t>
+          <t>2313</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>同欣電</t>
+          <t>華通</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>686,000</t>
+          <t>329,000</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>0.06%</t>
+          <t>0.03%</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>2002</t>
+          <t>1319</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>中鋼</t>
+          <t>東陽</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>5,163,000</t>
+          <t>511,000</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
         <is>
-          <t>0.04%</t>
+          <t>0.02%</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>2313</t>
+          <t>3661</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>華通</t>
+          <t>世芯-KY</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>329,000</t>
+          <t>1,000</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>0.03%</t>
+          <t>0.00%</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>1319</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>東陽</t>
+          <t>世界</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>511,000</t>
+          <t>1,000</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr">
         <is>
-          <t>0.02%</t>
+          <t>0.00%</t>
         </is>
       </c>
     </row>
@@ -1591,17 +1591,17 @@
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>2439</t>
+          <t>3264</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>美律</t>
+          <t>欣銓</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>18,000</t>
+          <t>1,000</t>
         </is>
       </c>
       <c r="D66" s="4" t="inlineStr">
@@ -1613,17 +1613,17 @@
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>2481</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>廣達</t>
+          <t>強茂</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>1,000</t>
+          <t>5,000</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
@@ -1635,12 +1635,12 @@
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>3008</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>世界</t>
+          <t>大立光</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
@@ -1657,17 +1657,17 @@
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>3661</t>
+          <t>2439</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>世芯-KY</t>
+          <t>美律</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>1,000</t>
+          <t>18,000</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr">
@@ -1679,12 +1679,12 @@
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>3264</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>欣銓</t>
+          <t>廣達</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
@@ -1701,46 +1701,38 @@
     <row r="71">
       <c r="A71" s="3" t="inlineStr">
         <is>
-          <t>2481</t>
+          <t>C_NTD</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>強茂</t>
+          <t>CASH</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>5,000</t>
-        </is>
-      </c>
-      <c r="D71" s="4" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
+          <t>4,563,458,507</t>
+        </is>
+      </c>
+      <c r="D71" s="4" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="3" t="inlineStr">
         <is>
-          <t>3008</t>
+          <t>M_NTD</t>
         </is>
       </c>
       <c r="B72" s="3" t="inlineStr">
         <is>
-          <t>大立光</t>
+          <t>MARGIN</t>
         </is>
       </c>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t>1,000</t>
-        </is>
-      </c>
-      <c r="D72" s="4" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
+          <t>500,128,241</t>
+        </is>
+      </c>
+      <c r="D72" s="4" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="3" t="inlineStr">
@@ -1758,11 +1750,7 @@
           <t>-1,648,000,714</t>
         </is>
       </c>
-      <c r="D73" s="4" t="inlineStr">
-        <is>
-          <t>-0.60%</t>
-        </is>
-      </c>
+      <c r="D73" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="5">
